--- a/变电站/2026年7月/收据/402房_7月收据.xlsx
+++ b/变电站/2026年7月/收据/402房_7月收据.xlsx
@@ -713,22 +713,24 @@
         <v>4548</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>4619</v>
+        <v>4691</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
+      <c r="H6" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="I6" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" s="9" t="n"/>
     </row>
@@ -809,7 +811,7 @@
     <row r="10" ht="28" customHeight="1" s="5">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>合计   人民币（大写）壹仟零肆拾柒元整</t>
+          <t>合计   人民币（大写）壹仟壹佰壹拾玖元整</t>
         </is>
       </c>
       <c r="B10" s="14" t="n"/>
@@ -821,7 +823,7 @@
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>(¥：1047元)</t>
+          <t>(¥：1119元)</t>
         </is>
       </c>
       <c r="J10" s="14" t="n"/>
